--- a/2022 data/excel_outputs/178_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/178_boothwise_data.xlsx
@@ -14,72 +14,186 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="443">
   <si>
     <t>AC 178 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0### ###### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0#### ####### #0 ###### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ########### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ########### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0### ######## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ###### atirikt ####</t>
-  </si>
-  <si>
-    <t>####0### ##### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ######### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ###### ##### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ###### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0### #### ##### #### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ####### ####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##0 3</t>
+    <t>PS KHARAWA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PURE DRAGPAL H/O KHARAVA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS HATHROHNA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS NAGIYAMAU R.N.1</t>
+  </si>
+  <si>
+    <t>PS KUKHARAMP UR R.N.1</t>
+  </si>
+  <si>
+    <t>PS KUKHARAMP UR R.N.2</t>
+  </si>
+  <si>
+    <t>PS KUSHUMBHI R.N.1</t>
+  </si>
+  <si>
+    <t>PS JAITPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS SAKATPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS TIKARI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS JAGATPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS LAULI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS LAULI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MEHMANPU R R.N.1</t>
+  </si>
+  <si>
+    <t>PS BASANTPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS KOTWA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KOTWA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS DIGHIYA KOTWA R.N.1</t>
+  </si>
+  <si>
+    <t>PS NAUKHEDA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS ANGURI R.N.1</t>
+  </si>
+  <si>
+    <t>PS ANGURI R.N.2</t>
+  </si>
+  <si>
+    <t>PS CHILAULI R.N.1</t>
+  </si>
+  <si>
+    <t>PS CHILAULI R.N.2</t>
+  </si>
+  <si>
+    <t>PS CHAUNAPUR INHAUNA R.N.1</t>
+  </si>
+  <si>
+    <t>PS INHAUNA R.N.1</t>
+  </si>
+  <si>
+    <t>PS INHAUNA R.N.2</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 1</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 2</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 3</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 4</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 5</t>
+  </si>
+  <si>
+    <t>G.I.C INHNAUNA R.N. 6</t>
   </si>
   <si>
     <t>raaj0iN0kaa0inhaunaa kkss sNkhyaa-1</t>
@@ -100,145 +214,214 @@
     <t>raaj0iN0kaa0inhaunaa kkss sNkhyaa-6</t>
   </si>
   <si>
-    <t>####0##0 ######## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ######## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>##0##0##### ######### #### ##nn1</t>
-  </si>
-  <si>
-    <t>##0##0##### ######### #### ##nn#</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### #### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0### #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### ##### ########## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0### ##### ########## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ######## #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0### ######## #### ##nn 3</t>
+    <t>PS SATANPURW A R.N.1</t>
+  </si>
+  <si>
+    <t>PS SATANPURW A R.N.2</t>
+  </si>
+  <si>
+    <t>JHS SATANPURW A R.N. 1</t>
+  </si>
+  <si>
+    <t>JHS SATANPURW A R.N. 2</t>
+  </si>
+  <si>
+    <t>PS BHANIPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BHANIPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS TEDHAI R.N.1</t>
+  </si>
+  <si>
+    <t>PS TEDHAI R.N.2</t>
+  </si>
+  <si>
+    <t>PS MAHIYA SENDURIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS MAHESHPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS GOYAN R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PENDARA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PENDARA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PEDARIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS KHEKHARUW A R.N.1</t>
+  </si>
+  <si>
+    <t>PS JEHTA USRAHA R.N.1</t>
+  </si>
+  <si>
+    <t>PS SHIVRATANG ANJ JEHTA USRAHA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KHARAGPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RATWALIYA MANJHAR R.N.1</t>
+  </si>
+  <si>
+    <t>PS RATWALIYA MANJHAR R.N.2</t>
+  </si>
+  <si>
+    <t>PS KHARA R.N.1</t>
+  </si>
+  <si>
+    <t>PS KHARA R.N.2</t>
+  </si>
+  <si>
+    <t>PS KHARA R.N.3</t>
+  </si>
+  <si>
+    <t>PS PADHRAWA H/O KHARA R.N.1</t>
   </si>
   <si>
     <t>praa0vi0 peddriyaa kkss sNkhyaa 1</t>
   </si>
   <si>
-    <t>####0### ##### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ######### ##### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##nn#</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ##nn 3</t>
+    <t>JHS SINGHPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>JHS SINGHPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PANHAUNA (I) R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PANHAUNA(I ) R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PANHAUNA(I I) R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PANHAUNA(I I) R.N. 2</t>
+  </si>
+  <si>
+    <t>PS RAMGANJ R.N.1</t>
+  </si>
+  <si>
+    <t>PS AHORWA BHAVANI R.N.1</t>
+  </si>
+  <si>
+    <t>PS AHMDABAD PIPRI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS AHMDABAD PIPRI R.N. 2</t>
   </si>
   <si>
     <t>aaNgnbaaddii bhvn khaaraa</t>
   </si>
   <si>
-    <t>####0##0 ###### #0 #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ######## ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ######## ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### #### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>##0##0 ##### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##nn #</t>
+    <t>PS OTIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS AZADPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS AZADPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS AZADPUR R.N. 3</t>
+  </si>
+  <si>
+    <t>PS AZADPUR R.N. 4</t>
+  </si>
+  <si>
+    <t>PS SADHIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS SADHIYA R.N.2</t>
+  </si>
+  <si>
+    <t>PS JIYAPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS BAHUA R.N. 1</t>
+  </si>
+  <si>
+    <t>JHS BAHUA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MIRJAGARH R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MIRJAGARH R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MATTEPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MATTEPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS KARANGAO R.N.1</t>
+  </si>
+  <si>
+    <t>PS KARANGAO R.N.2</t>
+  </si>
+  <si>
+    <t>PS KARANGAO R.N.3</t>
+  </si>
+  <si>
+    <t>PS YUSUFNAGA R R.N.1</t>
+  </si>
+  <si>
+    <t>PS YUSUFNAGA R R.N.2</t>
+  </si>
+  <si>
+    <t>PS SHEKHANGA O R.N.1</t>
+  </si>
+  <si>
+    <t>PS SHEKHANGA O R.N.2</t>
+  </si>
+  <si>
+    <t>PS FATTEPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS FATTEPUR R.N.2</t>
+  </si>
+  <si>
+    <t>G.I.C FATTEPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS RAJAPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS RAJAPUR R.N.2</t>
+  </si>
+  <si>
+    <t>PS JAYNAGRA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS JUGRAJPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RUKUNPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS RUKUNPUR R.N.2</t>
+  </si>
+  <si>
+    <t>PS GODHANA R.N.1</t>
+  </si>
+  <si>
+    <t>PS GAUDA DANDUPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS GAUDA DANDUPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS RAMPUR PAVARA R.N. 1</t>
   </si>
   <si>
     <t>praa0vi0 yusuphngr atirikt kkss sNkhyaa-1</t>
@@ -247,28 +430,79 @@
     <t>praa0vi0 yusuphngr atirikt kkss sNkhyaa-2</t>
   </si>
   <si>
-    <t>####0##0 ######## #### sN 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #### ##nn#</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ###### ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ###### ###### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #### ##nn#</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ####### #### ##nn #</t>
+    <t>JHS SEMRAUTA R.N.1</t>
+  </si>
+  <si>
+    <t>JHS SEMRAUTA R.N.2</t>
+  </si>
+  <si>
+    <t>PS SEMRAUTA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SEMRAUTA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS BASANTPUR R.N.2</t>
+  </si>
+  <si>
+    <t>PS SATGAVA KISHUNPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS SATGAVA KISHUNPUR R.N.2</t>
+  </si>
+  <si>
+    <t>PS THOKARPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS THOKARPUR R.N.2</t>
+  </si>
+  <si>
+    <t>PS AKABAR FARSHI R.N.1</t>
+  </si>
+  <si>
+    <t>PS RAJAPUR HALEEM R.N.1</t>
+  </si>
+  <si>
+    <t>JHS FOOLA R.N.1</t>
+  </si>
+  <si>
+    <t>JHS FOOLA R.N.2</t>
+  </si>
+  <si>
+    <t>JHS FOOLA R.N.3</t>
+  </si>
+  <si>
+    <t>JHS FOOLA R.N.4</t>
+  </si>
+  <si>
+    <t>PS SHUKLAPUR FOOLA R.N.1</t>
+  </si>
+  <si>
+    <t>PS SHUKLAPUR FOOLA R.N.2</t>
+  </si>
+  <si>
+    <t>PS HASANPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS KONCHI R.N.1</t>
+  </si>
+  <si>
+    <t>PS KHANAPUR CHAPRA R.N.1</t>
+  </si>
+  <si>
+    <t>PS KHANAPUR CHAPRA R.N.2</t>
+  </si>
+  <si>
+    <t>PS KHANAPUR CHAPRA R.N.3</t>
+  </si>
+  <si>
+    <t>PS KHANAPUR CHAPRA R.N.4</t>
+  </si>
+  <si>
+    <t>PS RASTAMAU R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RASTAMAU R.N. 2</t>
   </si>
   <si>
     <t>ucc praathmik vidyaaly pttkhaulii (bsntpur) kkss sNkhyaa-6</t>
@@ -277,52 +511,76 @@
     <t>ucc praathmik vidyaaly pttkhaulii (bsntpur) kkss sNkhyaa-7</t>
   </si>
   <si>
-    <t>####0### ###### ######## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ###### ######## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>##0### ##### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### atirikt ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##nn#</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ## 3</t>
-  </si>
-  <si>
-    <t>##0 ##0##### ####### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### ####### #### ##nn1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ##nn#</t>
+    <t>PS ERI RASTAMAU R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RAJANPUR R.N.1</t>
+  </si>
+  <si>
+    <t>SPN INTER TILOI R.N.1</t>
+  </si>
+  <si>
+    <t>SPN INTER TILOI R.N.2</t>
+  </si>
+  <si>
+    <t>PS TILOI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS TILOI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PASHCHIM TILOI R.N.1</t>
+  </si>
+  <si>
+    <t>PS SANGIPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KUTMARA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS DEVKALI R.N.1</t>
+  </si>
+  <si>
+    <t>PS CHILULI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS CHILULI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS BHAVAN NAGAR R.N.1</t>
+  </si>
+  <si>
+    <t>P.S.VINDHA DEEVAN R.N.1</t>
+  </si>
+  <si>
+    <t>PS KAMAI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KAMAI R.N. 2</t>
+  </si>
+  <si>
+    <t>P.S. BHADMAR R.N.1</t>
+  </si>
+  <si>
+    <t>P.S.BHADMA R R.N.2</t>
+  </si>
+  <si>
+    <t>P.S.GOKULA VIRAJ R.N.1</t>
+  </si>
+  <si>
+    <t>P.S.GOKULA VIRAJ R.N.2</t>
+  </si>
+  <si>
+    <t>PS REVTEDEEH R.N.1</t>
+  </si>
+  <si>
+    <t>PS RAMNAGAR R.N.1</t>
+  </si>
+  <si>
+    <t>PS KISHUNPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS ASHAPUR GADI R.N.1</t>
   </si>
   <si>
     <t>es0 pii0en0i0kaa0tilori kkss sN 1</t>
@@ -331,88 +589,121 @@
     <t>es0 pii0en0i0kaa0tilori kkss s 2</t>
   </si>
   <si>
-    <t>#### ## ## ##0 ##### #### ##nn3</t>
-  </si>
-  <si>
-    <t>#### ## ## ##0 ##### #### ##nn 4</t>
+    <t>PS BHADSANA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS ONDEEH R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SIJNI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS UTTARPARA R.N. 1</t>
   </si>
   <si>
     <t>praa0vi0 pshicm tilori atirikt kkss</t>
   </si>
   <si>
-    <t>####0 ##0 ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0 ### ########## ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>####0### ###### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>juu0haa0skuul ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>juu0haa0skuul ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>juu0haa0skuul ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0####### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0####### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>dyaannd i0kaa0 ###### ##### #### ##nn 1</t>
-  </si>
-  <si>
-    <t>dyaannd i0kaa0 ###### ##### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>dyaannd i0kaa0 ###### ##### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0########### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0###### #### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0###### #### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0######## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0######## #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### #### ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ###aa## #### ## #</t>
-  </si>
-  <si>
-    <t>####0### ###aa## #### ## 2</t>
-  </si>
-  <si>
-    <t>####0### ##### kkss sN 1</t>
-  </si>
-  <si>
-    <t>####0### ##### kkss sN 2</t>
+    <t>PS CHHICHHA R.N. 1</t>
+  </si>
+  <si>
+    <t>JHS ALAIPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BADHAUNA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BESARVA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS POORE MANIMANO HAR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PAKARGOV R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PAKARGOV R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PAKARGOV NEW BHAVAN R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SATWA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RAMAI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RAMAI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS BARKOT R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BARKOT R.N. 2</t>
+  </si>
+  <si>
+    <t>PANCHAYAT GHAR SAIMBASI R.N. 1</t>
+  </si>
+  <si>
+    <t>PANCHAYAT GHAR SAIMBASI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS SAVITAPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS BARDHARME R.N. 1</t>
+  </si>
+  <si>
+    <t>PS CHETRA BUJURG R.N.1</t>
+  </si>
+  <si>
+    <t>PS MOHANGAN J R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MOHANGAN J R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOHANGAN J R.N. 3</t>
+  </si>
+  <si>
+    <t>PS MOHANGAN J R.N. 4</t>
+  </si>
+  <si>
+    <t>PS BHELAIKHUR D R.N. 1</t>
+  </si>
+  <si>
+    <t>PS PURE KASHIRAM H/O LODHWARIY A</t>
+  </si>
+  <si>
+    <t>PS NASRATPUR R.N.1</t>
+  </si>
+  <si>
+    <t>PS RAJAMAU R.N. 1</t>
+  </si>
+  <si>
+    <t>PS RAJAMAU R.N. 2</t>
   </si>
   <si>
     <t>aadrsh baal kenidrt praa0vi0 uttrpaaraa</t>
   </si>
   <si>
-    <t>####0######### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### #### ######## #### ##nn #</t>
+    <t>PS ARIYAVA R.N.1</t>
+  </si>
+  <si>
+    <t>PS ARIYAVA R.N.2</t>
+  </si>
+  <si>
+    <t>PS KHANAPUR BAN R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SHANKARGA NJ CHHATAHU WA R.N.1</t>
+  </si>
+  <si>
+    <t>PS SHANKARGA NJ CHHATAHU WA R.N.2</t>
+  </si>
+  <si>
+    <t>PS MEDHAUNA R.N. 1</t>
   </si>
   <si>
     <t>puurv maadhymik vi0paakrgaaNv u0kkss</t>
@@ -421,7 +712,13 @@
     <t>puurv maadhymik vi0paakrgaaNv d0kkss</t>
   </si>
   <si>
-    <t>####0### ######## #### ### #### ##nn #</t>
+    <t>PS JAMURWA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS HARIHARPU R JAMURWA R.N.1</t>
+  </si>
+  <si>
+    <t>PS TODARPUR R.N.1</t>
   </si>
   <si>
     <t>puurv maadhymik vi0 rmri kkss sN0-1</t>
@@ -430,6 +727,12 @@
     <t>puurv maadhymik vi0 rmri kkss sN0-2</t>
   </si>
   <si>
+    <t>PS ASNI R.N.1</t>
+  </si>
+  <si>
+    <t>G. PS HASWA R.N. 1</t>
+  </si>
+  <si>
     <t>puurv maadhymik vidyaaly saimbsii kkss sNkhyaa-1</t>
   </si>
   <si>
@@ -439,64 +742,142 @@
     <t>praa0vi0ackvaapur kkss sN 1</t>
   </si>
   <si>
-    <t>####0### ############ #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### ############ #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn 3</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn 4</t>
-  </si>
-  <si>
-    <t>####0### ####### #### ##nn 5</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### #nn ######### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### #### ####### #0 ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0########### #### ##nn 2</t>
-  </si>
-  <si>
-    <t>####0### ####### ## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0########## ####### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0########## ####### atirikt ####</t>
-  </si>
-  <si>
-    <t>####0######### ######## ####</t>
-  </si>
-  <si>
-    <t>####0### ###### ######## ####</t>
-  </si>
-  <si>
-    <t>####0### ######## ###### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0########## #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0### puure baisn kkss sN 1</t>
-  </si>
-  <si>
-    <t>####0### puure baisn kkss sN 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ##nn #</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ##nn 2</t>
+    <t>PS NARAYANPU R R.N. 1</t>
+  </si>
+  <si>
+    <t>PS DHODHANP UR R.N.1</t>
+  </si>
+  <si>
+    <t>PS DHODHANP UR R.N.2</t>
+  </si>
+  <si>
+    <t>PS AHURI R.N.1</t>
+  </si>
+  <si>
+    <t>PS AHURI R.N.2</t>
+  </si>
+  <si>
+    <t>JHS AHURI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS LEEHI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BERARA R.N.1</t>
+  </si>
+  <si>
+    <t>PS BERARA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MIRAMAU R.N. 1</t>
+  </si>
+  <si>
+    <t>PS TAMAMAU R.N.1</t>
+  </si>
+  <si>
+    <t>PS BHAGIRATHP UR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BHAGIRATHP UR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS SHAHMAU R.N.1</t>
+  </si>
+  <si>
+    <t>PS BELWAHASA NPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS JANAPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS AGAUNA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS AGOUNA R.N. 2</t>
+  </si>
+  <si>
+    <t>J.H.S. JAIS R.N. 1</t>
+  </si>
+  <si>
+    <t>J.H.S.JAIS R.N. 2</t>
+  </si>
+  <si>
+    <t>JHS JAIS R.N. 3</t>
+  </si>
+  <si>
+    <t>JHS JAIS R.N. 4</t>
+  </si>
+  <si>
+    <t>JHS JAIS R.N. 5</t>
+  </si>
+  <si>
+    <t>JHS JAIS R.N. 6</t>
+  </si>
+  <si>
+    <t>PS JAIS II R.N. 1</t>
+  </si>
+  <si>
+    <t>PS JAIS R.N. 2</t>
+  </si>
+  <si>
+    <t>GGIC JAIS R.N. 1</t>
+  </si>
+  <si>
+    <t>GGIC JAIS R.N. 2</t>
+  </si>
+  <si>
+    <t>GGIC JAIS R.N. 3</t>
+  </si>
+  <si>
+    <t>GGIC JAIS R.N. 4</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 1</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 2</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 3</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 4</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 5</t>
+  </si>
+  <si>
+    <t>GIC JAIS R.N. 6</t>
+  </si>
+  <si>
+    <t>PS JAIS R.N. 1</t>
+  </si>
+  <si>
+    <t>PS JAIS R.N. 3</t>
+  </si>
+  <si>
+    <t>PS MOLVI KHURD R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOLVI KHURD R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MOLVI KHURD R.N. 3</t>
+  </si>
+  <si>
+    <t>MALK MOHD JAIS R.N. 1</t>
+  </si>
+  <si>
+    <t>MALIK MOHD JAIS R.N. 2</t>
+  </si>
+  <si>
+    <t>MALIK MOHD JAIS R.N. 3</t>
+  </si>
+  <si>
+    <t>MALIK MOHD JAIS R.N. 4</t>
+  </si>
+  <si>
+    <t>MALIK MOHD JAIS R.N. 5</t>
   </si>
   <si>
     <t>srdaar pttel iNttr kaalej ahurii kkss sN0 1</t>
@@ -505,37 +886,37 @@
     <t>srdaar pttel iNttr kaalej ahurii kkss sN0 2</t>
   </si>
   <si>
-    <t>####0 ##0#### #### ##nn #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ### #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0######### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0######### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ### raajaapur ########### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### raajaapur ########### #### ##0 2</t>
+    <t>PS NAGDEIYAP UR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BAHADURPU R R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BAHADURPU R R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MAVAI ALAMPUR R.N.1</t>
+  </si>
+  <si>
+    <t>HARIBANSH GANJ</t>
+  </si>
+  <si>
+    <t>PS HARIBANSH GANJ R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MUBARAKP UR MUKHETIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS MUBARAKP UR MUKHETIYA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PURE BADERAY R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOHNA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOHNA R.N. 2</t>
   </si>
   <si>
     <t>aaNgnbaaddii kendr jnaapur kkss sNkhyaa-1</t>
@@ -544,40 +925,46 @@
     <t>atirikt kkss praa0vi0 jnaapur</t>
   </si>
   <si>
-    <t>##0 ##0 ##### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #### ##0 6</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0#0##0 #### #### ### 1</t>
-  </si>
-  <si>
-    <t>##0#0#0##0 #### #### ### 7</t>
-  </si>
-  <si>
-    <t>##0#0#0##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0#0##0 #### #### ##0 3</t>
+    <t>PS UDAVA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS UDAVA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS NAVAVA R.N.1</t>
+  </si>
+  <si>
+    <t>PS NAVAVA R.N. 2</t>
+  </si>
+  <si>
+    <t>PS VIJAYPUR PIDHI R.N.1</t>
+  </si>
+  <si>
+    <t>PS VIJAYPUR PIDHI R.N. 2</t>
+  </si>
+  <si>
+    <t>JHS PIDHI R.N. 1</t>
+  </si>
+  <si>
+    <t>JHS PIDHI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS PIDHI R.N. 3</t>
+  </si>
+  <si>
+    <t>JHS PIDHI R.N. 4</t>
+  </si>
+  <si>
+    <t>PS BHADEHRA R.N.1</t>
+  </si>
+  <si>
+    <t>PS KHALISPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KHALISPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS MAHMADPU R R.N. 1</t>
   </si>
   <si>
     <t>kmpojitt skuul maa0 kaashiiraam shhrii dlit bstii saidaanaa jaays kkss sNkhyaa-1</t>
@@ -589,37 +976,37 @@
     <t>kmpojitt skuul maa0 kaashiiraam shhrii dlit bstii saidaanaa jaays kkss sNkhyaa-3</t>
   </si>
   <si>
-    <t>##0#0##0 #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0#0##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0##0 #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0#0##0 #### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0#0##0 #### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0#0##0 #### #### ##0 6</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ### ##### ##### #### ##0 2</t>
+    <t>PS TARAUNA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SARVAN R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SARVAN R.2</t>
+  </si>
+  <si>
+    <t>PS KISHUNPUR KEVAI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KISHUNPUR KEVAI R.N. 2</t>
+  </si>
+  <si>
+    <t>PS SAIMBSHI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOHAIYA KESARIYA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS MOHAIYA KESARIYA R.N.2</t>
+  </si>
+  <si>
+    <t>KJSH FURSATGANJ R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BRAHMANI R.N. 1</t>
+  </si>
+  <si>
+    <t>PS BRAHMANI R.N. 2</t>
   </si>
   <si>
     <t>praa0vi0 molviiklaa kkss sNkhyaa-1</t>
@@ -628,223 +1015,262 @@
     <t>praa0vi0 molviiklaa kkss sNkhyaa-2</t>
   </si>
   <si>
-    <t>#### ##0 ##### #0##0 #### ##01</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### #0##0 #### ###2</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### #0##0 #### ##03</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### #0##0 #### ##04</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### #0##0 #### ##0 5</t>
-  </si>
-  <si>
-    <t>#### ##0 ##### #0##0 #### ##06</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ######## #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ### ########## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ######### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ######### #### ##0 2</t>
+    <t>PS NIGOHAN R.N. 2</t>
+  </si>
+  <si>
+    <t>PS NIGOHAN R.N. 3</t>
+  </si>
+  <si>
+    <t>PS KESARIYA SALEEMPUR R.N. 1</t>
+  </si>
+  <si>
+    <t>PS KESARIYA SALEEMPUR R.N. 2</t>
+  </si>
+  <si>
+    <t>PS FARIDPUR PARVAR R.N 1</t>
+  </si>
+  <si>
+    <t>PS DAULATPUR SINGHARIYA R.N.1</t>
+  </si>
+  <si>
+    <t>PS SARAY MAHESHA R.N. 1</t>
+  </si>
+  <si>
+    <t>PS SARAY MAHESHA R.N. 1 ROOM NO. 318</t>
+  </si>
+  <si>
+    <t>PS SARAY MAHESHA R.N. 1 ROOM ROOM NO. 319</t>
+  </si>
+  <si>
+    <t>PS SARAY MAHESHA R.N. 1 ROOM ROOM ROOM NO. 320</t>
+  </si>
+  <si>
+    <t>PS SARAY MAHESHA R.N. 1 ROOM ROOM ROOM ROOM NO. 321</t>
   </si>
   <si>
     <t>atirikt kkss praa0vi0 mvri aalmpur</t>
   </si>
   <si>
-    <t>##0##0 ##### #########</t>
-  </si>
-  <si>
-    <t>####0 ### ######### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ############ ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ### #### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##### kkss sN 1</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##### kkss sN 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### atirikt ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ########### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>praa0vi0 ####### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>praa0vi0 ####### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### #### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### #### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ### ######## #### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ######## #### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ##01</t>
-  </si>
-  <si>
-    <t>kmpojitt skuul ###### ####### #### ##01</t>
-  </si>
-  <si>
-    <t>kmpojitt skuul ###### ####### #### ##02</t>
-  </si>
-  <si>
-    <t>#0##0 ##0 ##### ######## #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ########## #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ##03</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### ### 3</t>
-  </si>
-  <si>
-    <t>####0 ### ####### ####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ####### ####### #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ####### #### #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### ####### ######### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ####### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ####### ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ####### ##### #### ### 3</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### #### #####</t>
-  </si>
-  <si>
-    <t>juuniyr haariskuul ###### #### ## 1</t>
-  </si>
-  <si>
-    <t>juuniyr haariskuul ###### #### ## 2</t>
-  </si>
-  <si>
-    <t>####0 ### ###### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ##### ######## #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ##0##### ######## #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### ###### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ####### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ####### ##### #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### #### #### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### #### #### ##### atirikt ####</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### ### 3</t>
-  </si>
-  <si>
-    <t>####0 ######### #### ##01</t>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM NO. 323</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM NO. 324</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM NO. 325</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM NO. 326</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM NO. 327</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM NO. 328</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 329</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 330</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 331</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 332</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 333</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 334</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 335</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 336</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 337</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 338</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 339</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 342</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 343</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 344</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>atirikt kkss praa0vi0 mvri aalmpur ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
   </si>
   <si>
     <t>praa0 vi0 bghail kkss sN0 1</t>
   </si>
   <si>
-    <t>praa0 vi0 khraulii #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ##### ####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0 ### ##### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ### #### ###### #### ##nn#</t>
+    <t>praa0 vi0 bghail kkss sN0 1 ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>praa0 vi0 bghail kkss sN0 1 ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>praa0 vi0 bghail kkss sN0 1 ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>praa0 vi0 bghail kkss sN0 1 ROOM ROOM ROOM ROOM NO. 396</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -923,8 +1349,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -940,7 +1374,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -948,12 +1382,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1252,88 +1704,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>277</v>
+        <v>419</v>
       </c>
       <c r="D2" t="s">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>421</v>
       </c>
       <c r="F2" t="s">
-        <v>280</v>
+        <v>422</v>
       </c>
       <c r="G2" t="s">
-        <v>281</v>
+        <v>423</v>
       </c>
       <c r="H2" t="s">
-        <v>282</v>
+        <v>424</v>
       </c>
       <c r="I2" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="J2" t="s">
-        <v>284</v>
+        <v>426</v>
       </c>
       <c r="K2" t="s">
-        <v>285</v>
+        <v>427</v>
       </c>
       <c r="L2" t="s">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="M2" t="s">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="N2" t="s">
-        <v>288</v>
+        <v>430</v>
       </c>
       <c r="O2" t="s">
-        <v>289</v>
+        <v>431</v>
       </c>
       <c r="P2" t="s">
-        <v>290</v>
+        <v>432</v>
       </c>
       <c r="Q2" t="s">
-        <v>291</v>
+        <v>433</v>
       </c>
       <c r="R2" t="s">
-        <v>292</v>
+        <v>434</v>
       </c>
       <c r="S2" t="s">
-        <v>293</v>
+        <v>435</v>
       </c>
       <c r="T2" t="s">
-        <v>294</v>
+        <v>436</v>
       </c>
       <c r="U2" t="s">
-        <v>295</v>
+        <v>437</v>
       </c>
       <c r="V2" t="s">
-        <v>296</v>
+        <v>438</v>
       </c>
       <c r="W2" t="s">
-        <v>297</v>
+        <v>439</v>
       </c>
       <c r="X2" t="s">
-        <v>298</v>
+        <v>440</v>
       </c>
       <c r="Y2" t="s">
-        <v>299</v>
+        <v>441</v>
       </c>
       <c r="Z2" t="s">
-        <v>300</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1341,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1061</v>
@@ -1421,7 +1948,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>726</v>
@@ -1501,7 +2028,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -1581,7 +2108,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>546</v>
@@ -1661,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1131</v>
@@ -1741,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>731</v>
@@ -1821,7 +2348,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>716</v>
@@ -1901,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>709</v>
@@ -1981,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>793</v>
@@ -2061,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>717</v>
@@ -2141,7 +2668,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>394</v>
@@ -2221,7 +2748,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>669</v>
@@ -2301,7 +2828,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>780</v>
@@ -2381,7 +2908,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>1004</v>
@@ -2461,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>981</v>
@@ -2541,7 +3068,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>901</v>
@@ -2621,7 +3148,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>1036</v>
@@ -2701,7 +3228,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>1118</v>
@@ -2781,7 +3308,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>823</v>
@@ -2861,7 +3388,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>1026</v>
@@ -2941,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>793</v>
@@ -3021,7 +3548,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>588</v>
@@ -3101,7 +3628,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>1040</v>
@@ -3181,7 +3708,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>862</v>
@@ -3261,7 +3788,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>924</v>
@@ -3341,7 +3868,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>1049</v>
@@ -3421,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>725</v>
@@ -3501,7 +4028,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>666</v>
@@ -3581,7 +4108,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>835</v>
@@ -3661,7 +4188,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>891</v>
@@ -3741,7 +4268,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>1028</v>
@@ -3821,7 +4348,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>625</v>
@@ -3901,7 +4428,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>946</v>
@@ -3981,7 +4508,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>1053</v>
@@ -4061,7 +4588,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>1015</v>
@@ -4141,7 +4668,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>925</v>
@@ -4221,7 +4748,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>1137</v>
@@ -4301,7 +4828,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>1074</v>
@@ -4381,7 +4908,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>846</v>
@@ -4461,7 +4988,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>566</v>
@@ -4541,7 +5068,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>685</v>
@@ -4621,7 +5148,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>550</v>
@@ -4701,7 +5228,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>899</v>
@@ -4781,7 +5308,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>956</v>
@@ -4861,7 +5388,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>966</v>
@@ -4941,7 +5468,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>1112</v>
@@ -5021,7 +5548,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>1175</v>
@@ -5101,7 +5628,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="C50">
         <v>787</v>
@@ -5181,7 +5708,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C51">
         <v>701</v>
@@ -5261,7 +5788,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="C52">
         <v>916</v>
@@ -5341,7 +5868,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>890</v>
@@ -5421,7 +5948,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>619</v>
@@ -5501,7 +6028,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>819</v>
@@ -5581,7 +6108,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="C56">
         <v>828</v>
@@ -5661,7 +6188,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>774</v>
@@ -5741,7 +6268,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="C58">
         <v>701</v>
@@ -5821,7 +6348,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>672</v>
@@ -5901,7 +6428,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C60">
         <v>807</v>
@@ -5981,7 +6508,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C61">
         <v>724</v>
@@ -6061,7 +6588,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C62">
         <v>954</v>
@@ -6141,7 +6668,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>924</v>
@@ -6221,7 +6748,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C64">
         <v>878</v>
@@ -6301,7 +6828,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>1090</v>
@@ -6381,7 +6908,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>740</v>
@@ -6461,7 +6988,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>858</v>
@@ -6541,7 +7068,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>1066</v>
@@ -6621,7 +7148,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="C69">
         <v>1026</v>
@@ -6701,7 +7228,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="C70">
         <v>1064</v>
@@ -6781,7 +7308,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="C71">
         <v>746</v>
@@ -6861,7 +7388,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>806</v>
@@ -6941,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>887</v>
@@ -7021,7 +7548,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="C74">
         <v>1039</v>
@@ -7101,7 +7628,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C75">
         <v>862</v>
@@ -7181,7 +7708,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>935</v>
@@ -7261,7 +7788,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>886</v>
@@ -7341,7 +7868,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>738</v>
@@ -7421,7 +7948,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>1035</v>
@@ -7501,7 +8028,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>940</v>
@@ -7581,7 +8108,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C81">
         <v>942</v>
@@ -7661,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="C82">
         <v>1184</v>
@@ -7741,7 +8268,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C83">
         <v>816</v>
@@ -7821,7 +8348,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>887</v>
@@ -7901,7 +8428,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>995</v>
@@ -7981,7 +8508,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>733</v>
@@ -8061,7 +8588,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>1034</v>
@@ -8141,7 +8668,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>991</v>
@@ -8221,7 +8748,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>1066</v>
@@ -8301,7 +8828,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>651</v>
@@ -8381,7 +8908,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>621</v>
@@ -8461,7 +8988,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>703</v>
@@ -8541,7 +9068,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>723</v>
@@ -8621,7 +9148,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>1084</v>
@@ -8701,7 +9228,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>1157</v>
@@ -8781,7 +9308,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>1065</v>
@@ -8861,7 +9388,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>1096</v>
@@ -8941,7 +9468,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>1065</v>
@@ -9021,7 +9548,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>588</v>
@@ -9101,7 +9628,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>1127</v>
@@ -9181,7 +9708,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>905</v>
@@ -9261,7 +9788,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>736</v>
@@ -9341,7 +9868,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>1058</v>
@@ -9421,7 +9948,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>1091</v>
@@ -9501,7 +10028,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>768</v>
@@ -9581,7 +10108,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>841</v>
@@ -9661,7 +10188,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>1129</v>
@@ -9741,7 +10268,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>658</v>
@@ -9821,7 +10348,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>1173</v>
@@ -9901,7 +10428,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>1069</v>
@@ -9981,7 +10508,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>410</v>
@@ -10061,7 +10588,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>859</v>
@@ -10141,7 +10668,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>765</v>
@@ -10221,7 +10748,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>1038</v>
@@ -10301,7 +10828,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>959</v>
@@ -10381,7 +10908,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>1107</v>
@@ -10461,7 +10988,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>735</v>
@@ -10541,7 +11068,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C118">
         <v>1076</v>
@@ -10621,7 +11148,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>887</v>
@@ -10701,7 +11228,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>899</v>
@@ -10781,7 +11308,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>877</v>
@@ -10861,7 +11388,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>918</v>
@@ -10941,7 +11468,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>623</v>
@@ -11021,7 +11548,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>641</v>
@@ -11101,7 +11628,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>1154</v>
@@ -11181,7 +11708,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>697</v>
@@ -11261,7 +11788,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>1068</v>
@@ -11341,7 +11868,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>944</v>
@@ -11421,7 +11948,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>793</v>
@@ -11501,7 +12028,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>964</v>
@@ -11581,7 +12108,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>753</v>
@@ -11661,7 +12188,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>759</v>
@@ -11741,7 +12268,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>1106</v>
@@ -11821,7 +12348,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>969</v>
@@ -11901,7 +12428,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>1099</v>
@@ -11981,7 +12508,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>770</v>
@@ -12061,7 +12588,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>952</v>
@@ -12141,7 +12668,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>648</v>
@@ -12221,7 +12748,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>1179</v>
@@ -12301,7 +12828,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1033</v>
@@ -12381,7 +12908,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>601</v>
@@ -12461,7 +12988,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>1003</v>
@@ -12541,7 +13068,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>846</v>
@@ -12621,7 +13148,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>1127</v>
@@ -12701,7 +13228,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>608</v>
@@ -12781,7 +13308,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>879</v>
@@ -12861,7 +13388,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>580</v>
@@ -12941,7 +13468,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>1126</v>
@@ -13021,7 +13548,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>911</v>
@@ -13101,7 +13628,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>844</v>
@@ -13181,7 +13708,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>907</v>
@@ -13261,7 +13788,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1012</v>
@@ -13341,7 +13868,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>792</v>
@@ -13421,7 +13948,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>903</v>
@@ -13501,7 +14028,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>1177</v>
@@ -13581,7 +14108,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>787</v>
@@ -13661,7 +14188,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>460</v>
@@ -13741,7 +14268,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1117</v>
@@ -13821,7 +14348,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>1065</v>
@@ -13901,7 +14428,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>1156</v>
@@ -13981,7 +14508,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>1197</v>
@@ -14061,7 +14588,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>1157</v>
@@ -14141,7 +14668,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>790</v>
@@ -14221,7 +14748,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>1105</v>
@@ -14301,7 +14828,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>926</v>
@@ -14381,7 +14908,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>744</v>
@@ -14461,7 +14988,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>742</v>
@@ -14541,7 +15068,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>766</v>
@@ -14621,7 +15148,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>1108</v>
@@ -14701,7 +15228,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>960</v>
@@ -14781,7 +15308,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>945</v>
@@ -14861,7 +15388,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>731</v>
@@ -14941,7 +15468,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>748</v>
@@ -15021,7 +15548,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>667</v>
@@ -15101,7 +15628,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>719</v>
@@ -15181,7 +15708,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>782</v>
@@ -15261,7 +15788,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>1129</v>
@@ -15341,7 +15868,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>1130</v>
@@ -15421,7 +15948,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>649</v>
@@ -15501,7 +16028,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>778</v>
@@ -15581,7 +16108,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>112</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>919</v>
@@ -15661,7 +16188,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1052</v>
@@ -15741,7 +16268,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>620</v>
@@ -15821,7 +16348,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>817</v>
@@ -15901,7 +16428,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>729</v>
@@ -15981,7 +16508,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>117</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>789</v>
@@ -16061,7 +16588,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>118</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>611</v>
@@ -16141,7 +16668,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>1024</v>
@@ -16221,7 +16748,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>439</v>
@@ -16301,7 +16828,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>1000</v>
@@ -16381,7 +16908,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>583</v>
@@ -16461,7 +16988,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>593</v>
@@ -16541,7 +17068,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>684</v>
@@ -16621,7 +17148,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>123</v>
+        <v>214</v>
       </c>
       <c r="C194">
         <v>899</v>
@@ -16701,7 +17228,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C195">
         <v>456</v>
@@ -16781,7 +17308,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="C196">
         <v>765</v>
@@ -16861,7 +17388,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="C197">
         <v>673</v>
@@ -16941,7 +17468,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="C198">
         <v>726</v>
@@ -17021,7 +17548,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>530</v>
@@ -17101,7 +17628,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>826</v>
@@ -17181,7 +17708,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>71</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>884</v>
@@ -17261,7 +17788,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>851</v>
@@ -17341,7 +17868,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>598</v>
@@ -17421,7 +17948,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>682</v>
@@ -17501,7 +18028,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>1108</v>
@@ -17581,7 +18108,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>1208</v>
@@ -17661,7 +18188,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>956</v>
@@ -17741,7 +18268,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>979</v>
@@ -17821,7 +18348,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>1189</v>
@@ -17901,7 +18428,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>1053</v>
@@ -17981,7 +18508,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>506</v>
@@ -18061,7 +18588,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>135</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>1105</v>
@@ -18141,7 +18668,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>1105</v>
@@ -18221,7 +18748,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>1029</v>
@@ -18301,7 +18828,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>602</v>
@@ -18381,7 +18908,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>63</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>889</v>
@@ -18461,7 +18988,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>63</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>759</v>
@@ -18541,7 +19068,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>1110</v>
@@ -18621,7 +19148,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>764</v>
@@ -18701,7 +19228,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>519</v>
@@ -18781,7 +19308,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>542</v>
@@ -18861,7 +19388,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>636</v>
@@ -18941,7 +19468,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>1013</v>
@@ -19021,7 +19548,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>1174</v>
@@ -19101,7 +19628,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>764</v>
@@ -19181,7 +19708,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>44</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>710</v>
@@ -19261,7 +19788,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>45</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>894</v>
@@ -19341,7 +19868,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>1096</v>
@@ -19421,7 +19948,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>905</v>
@@ -19501,7 +20028,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>1188</v>
@@ -19581,7 +20108,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>548</v>
@@ -19661,7 +20188,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>989</v>
@@ -19741,7 +20268,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>878</v>
@@ -19821,7 +20348,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>432</v>
@@ -19901,7 +20428,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>1001</v>
@@ -19981,7 +20508,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>63</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>846</v>
@@ -20061,7 +20588,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>585</v>
@@ -20141,7 +20668,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>120</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>1130</v>
@@ -20221,7 +20748,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>515</v>
@@ -20301,7 +20828,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>657</v>
@@ -20381,7 +20908,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>151</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>782</v>
@@ -20461,7 +20988,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>1028</v>
@@ -20541,7 +21068,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>907</v>
@@ -20621,7 +21148,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>131</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>1044</v>
@@ -20701,7 +21228,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>770</v>
@@ -20781,7 +21308,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>153</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>830</v>
@@ -20861,7 +21388,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>879</v>
@@ -20941,7 +21468,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>154</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>502</v>
@@ -21021,7 +21548,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>63</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>1069</v>
@@ -21101,7 +21628,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>1007</v>
@@ -21181,7 +21708,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>422</v>
@@ -21261,7 +21788,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>63</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>522</v>
@@ -21341,7 +21868,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>970</v>
@@ -21421,7 +21948,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>157</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>747</v>
@@ -21501,7 +22028,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>552</v>
@@ -21581,7 +22108,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>46</v>
+        <v>277</v>
       </c>
       <c r="C256">
         <v>791</v>
@@ -21661,7 +22188,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>41</v>
+        <v>278</v>
       </c>
       <c r="C257">
         <v>857</v>
@@ -21741,7 +22268,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="C258">
         <v>796</v>
@@ -21821,7 +22348,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>607</v>
@@ -21901,7 +22428,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>1103</v>
@@ -21981,7 +22508,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>46</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>1051</v>
@@ -22061,7 +22588,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>1174</v>
@@ -22141,7 +22668,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>353</v>
@@ -22221,7 +22748,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>39</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>1015</v>
@@ -22301,7 +22828,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>1086</v>
@@ -22381,7 +22908,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>1189</v>
@@ -22461,7 +22988,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>123</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>1095</v>
@@ -22541,7 +23068,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>161</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>489</v>
@@ -22621,7 +23148,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>916</v>
@@ -22701,7 +23228,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>163</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>1087</v>
@@ -22781,7 +23308,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>613</v>
@@ -22861,7 +23388,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>165</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>1011</v>
@@ -22941,7 +23468,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>166</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>1080</v>
@@ -23021,7 +23548,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>167</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>1150</v>
@@ -23101,7 +23628,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>168</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>1134</v>
@@ -23181,7 +23708,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>1031</v>
@@ -23261,7 +23788,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>977</v>
@@ -23341,7 +23868,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>171</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>626</v>
@@ -23421,7 +23948,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>610</v>
@@ -23501,7 +24028,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>801</v>
@@ -23581,7 +24108,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>174</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>933</v>
@@ -23661,7 +24188,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>546</v>
@@ -23741,7 +24268,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>170</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>1134</v>
@@ -23821,7 +24348,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>602</v>
@@ -23901,7 +24428,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>998</v>
@@ -23981,7 +24508,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>1023</v>
@@ -24061,7 +24588,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>1129</v>
@@ -24141,7 +24668,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>981</v>
@@ -24221,7 +24748,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>180</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>822</v>
@@ -24301,7 +24828,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>1021</v>
@@ -24381,7 +24908,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>1140</v>
@@ -24461,7 +24988,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>1138</v>
@@ -24541,7 +25068,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>659</v>
@@ -24621,7 +25148,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>710</v>
@@ -24701,7 +25228,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>622</v>
@@ -24781,7 +25308,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>626</v>
@@ -24861,7 +25388,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>767</v>
@@ -24941,7 +25468,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>714</v>
@@ -25021,7 +25548,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>1182</v>
@@ -25101,7 +25628,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>843</v>
@@ -25181,7 +25708,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>1125</v>
@@ -25261,7 +25788,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>1063</v>
@@ -25341,7 +25868,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>1042</v>
@@ -25421,7 +25948,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>996</v>
@@ -25501,7 +26028,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>196</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>651</v>
@@ -25581,7 +26108,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>976</v>
@@ -25661,7 +26188,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>1043</v>
@@ -25741,7 +26268,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>199</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>1102</v>
@@ -25821,7 +26348,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="C309">
         <v>1049</v>
@@ -25901,7 +26428,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="C310">
         <v>892</v>
@@ -25981,7 +26508,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="C311">
         <v>851</v>
@@ -26061,7 +26588,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>203</v>
+        <v>332</v>
       </c>
       <c r="C312">
         <v>954</v>
@@ -26141,7 +26668,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="C313">
         <v>748</v>
@@ -26221,7 +26748,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>205</v>
+        <v>334</v>
       </c>
       <c r="C314">
         <v>1013</v>
@@ -26301,7 +26828,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>206</v>
+        <v>335</v>
       </c>
       <c r="C315">
         <v>1094</v>
@@ -26381,7 +26908,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="C316">
         <v>1085</v>
@@ -26461,7 +26988,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
       <c r="C317">
         <v>1000</v>
@@ -26541,7 +27068,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="C318">
         <v>1014</v>
@@ -26621,7 +27148,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
       <c r="C319">
         <v>631</v>
@@ -26701,7 +27228,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="C320">
         <v>1015</v>
@@ -26781,7 +27308,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="C321">
         <v>856</v>
@@ -26861,7 +27388,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>213</v>
+        <v>342</v>
       </c>
       <c r="C322">
         <v>906</v>
@@ -26941,7 +27468,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>881</v>
@@ -27021,7 +27548,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="C324">
         <v>581</v>
@@ -27101,7 +27628,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>213</v>
+        <v>345</v>
       </c>
       <c r="C325">
         <v>910</v>
@@ -27181,7 +27708,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>216</v>
+        <v>346</v>
       </c>
       <c r="C326">
         <v>989</v>
@@ -27261,7 +27788,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>217</v>
+        <v>347</v>
       </c>
       <c r="C327">
         <v>705</v>
@@ -27341,7 +27868,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>218</v>
+        <v>348</v>
       </c>
       <c r="C328">
         <v>842</v>
@@ -27421,7 +27948,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>219</v>
+        <v>349</v>
       </c>
       <c r="C329">
         <v>1148</v>
@@ -27501,7 +28028,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="C330">
         <v>1135</v>
@@ -27581,7 +28108,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="C331">
         <v>1134</v>
@@ -27661,7 +28188,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>221</v>
+        <v>352</v>
       </c>
       <c r="C332">
         <v>1151</v>
@@ -27741,7 +28268,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="C333">
         <v>905</v>
@@ -27821,7 +28348,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="C334">
         <v>1115</v>
@@ -27901,7 +28428,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>224</v>
+        <v>355</v>
       </c>
       <c r="C335">
         <v>923</v>
@@ -27981,7 +28508,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>225</v>
+        <v>356</v>
       </c>
       <c r="C336">
         <v>1047</v>
@@ -28061,7 +28588,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>226</v>
+        <v>357</v>
       </c>
       <c r="C337">
         <v>998</v>
@@ -28141,7 +28668,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="C338">
         <v>1128</v>
@@ -28221,7 +28748,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>165</v>
+        <v>359</v>
       </c>
       <c r="C339">
         <v>1200</v>
@@ -28301,7 +28828,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>527</v>
@@ -28381,7 +28908,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>228</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>1024</v>
@@ -28461,7 +28988,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>176</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>940</v>
@@ -28541,7 +29068,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>1093</v>
@@ -28621,7 +29148,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>178</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>1063</v>
@@ -28701,7 +29228,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>1102</v>
@@ -28781,7 +29308,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>657</v>
@@ -28861,7 +29388,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>210</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>1081</v>
@@ -28941,7 +29468,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>956</v>
@@ -29021,7 +29548,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>1043</v>
@@ -29101,7 +29628,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>1108</v>
@@ -29181,7 +29708,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>951</v>
@@ -29261,7 +29788,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>233</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>923</v>
@@ -29341,7 +29868,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>234</v>
+        <v>373</v>
       </c>
       <c r="C353">
         <v>620</v>
@@ -29421,7 +29948,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>235</v>
+        <v>374</v>
       </c>
       <c r="C354">
         <v>1032</v>
@@ -29501,7 +30028,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="C355">
         <v>1040</v>
@@ -29581,7 +30108,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>237</v>
+        <v>376</v>
       </c>
       <c r="C356">
         <v>709</v>
@@ -29661,7 +30188,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="C357">
         <v>882</v>
@@ -29741,7 +30268,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>239</v>
+        <v>378</v>
       </c>
       <c r="C358">
         <v>992</v>
@@ -29821,7 +30348,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>240</v>
+        <v>379</v>
       </c>
       <c r="C359">
         <v>1132</v>
@@ -29901,7 +30428,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>241</v>
+        <v>380</v>
       </c>
       <c r="C360">
         <v>1116</v>
@@ -29981,7 +30508,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>242</v>
+        <v>381</v>
       </c>
       <c r="C361">
         <v>1019</v>
@@ -30061,7 +30588,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>243</v>
+        <v>382</v>
       </c>
       <c r="C362">
         <v>888</v>
@@ -30141,7 +30668,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>244</v>
+        <v>383</v>
       </c>
       <c r="C363">
         <v>905</v>
@@ -30221,7 +30748,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>245</v>
+        <v>384</v>
       </c>
       <c r="C364">
         <v>1145</v>
@@ -30301,7 +30828,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>239</v>
+        <v>385</v>
       </c>
       <c r="C365">
         <v>799</v>
@@ -30381,7 +30908,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="C366">
         <v>1097</v>
@@ -30461,7 +30988,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="C367">
         <v>1018</v>
@@ -30541,7 +31068,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="C368">
         <v>990</v>
@@ -30621,7 +31148,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="C369">
         <v>1099</v>
@@ -30701,7 +31228,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="C370">
         <v>819</v>
@@ -30781,7 +31308,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="C371">
         <v>438</v>
@@ -30861,7 +31388,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="C372">
         <v>656</v>
@@ -30941,7 +31468,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="C373">
         <v>1083</v>
@@ -31021,7 +31548,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>254</v>
+        <v>394</v>
       </c>
       <c r="C374">
         <v>888</v>
@@ -31101,7 +31628,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="C375">
         <v>439</v>
@@ -31181,7 +31708,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="C376">
         <v>1171</v>
@@ -31261,7 +31788,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>257</v>
+        <v>397</v>
       </c>
       <c r="C377">
         <v>675</v>
@@ -31341,7 +31868,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>258</v>
+        <v>398</v>
       </c>
       <c r="C378">
         <v>809</v>
@@ -31421,7 +31948,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>167</v>
+        <v>399</v>
       </c>
       <c r="C379">
         <v>808</v>
@@ -31501,7 +32028,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>259</v>
+        <v>400</v>
       </c>
       <c r="C380">
         <v>1095</v>
@@ -31581,7 +32108,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>260</v>
+        <v>401</v>
       </c>
       <c r="C381">
         <v>997</v>
@@ -31661,7 +32188,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>261</v>
+        <v>402</v>
       </c>
       <c r="C382">
         <v>1119</v>
@@ -31741,7 +32268,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>262</v>
+        <v>403</v>
       </c>
       <c r="C383">
         <v>1128</v>
@@ -31821,7 +32348,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>263</v>
+        <v>404</v>
       </c>
       <c r="C384">
         <v>1016</v>
@@ -31901,7 +32428,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="C385">
         <v>852</v>
@@ -31981,7 +32508,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>264</v>
+        <v>406</v>
       </c>
       <c r="C386">
         <v>1058</v>
@@ -32061,7 +32588,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>265</v>
+        <v>407</v>
       </c>
       <c r="C387">
         <v>463</v>
@@ -32141,7 +32668,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>266</v>
+        <v>408</v>
       </c>
       <c r="C388">
         <v>695</v>
@@ -32221,7 +32748,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>267</v>
+        <v>409</v>
       </c>
       <c r="C389">
         <v>718</v>
@@ -32301,7 +32828,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
       <c r="C390">
         <v>1130</v>
@@ -32381,7 +32908,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>269</v>
+        <v>411</v>
       </c>
       <c r="C391">
         <v>839</v>
@@ -32461,7 +32988,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>270</v>
+        <v>412</v>
       </c>
       <c r="C392">
         <v>878</v>
@@ -32541,7 +33068,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>271</v>
+        <v>413</v>
       </c>
       <c r="C393">
         <v>443</v>
@@ -32621,7 +33148,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>272</v>
+        <v>414</v>
       </c>
       <c r="C394">
         <v>893</v>
@@ -32701,7 +33228,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>273</v>
+        <v>415</v>
       </c>
       <c r="C395">
         <v>1117</v>
@@ -32781,7 +33308,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>274</v>
+        <v>416</v>
       </c>
       <c r="C396">
         <v>974</v>
@@ -32861,7 +33388,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="C397">
         <v>993</v>
@@ -32941,7 +33468,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>276</v>
+        <v>418</v>
       </c>
       <c r="C398">
         <v>939</v>
